--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129797328</v>
+        <v>129797332</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -800,33 +800,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743294</v>
+        <v>743452</v>
       </c>
       <c r="R3" t="n">
-        <v>7092958</v>
+        <v>7092954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129797332</v>
+        <v>129797328</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -913,17 +897,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743452</v>
+        <v>743294</v>
       </c>
       <c r="R4" t="n">
-        <v>7092954</v>
+        <v>7092958</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>129797334</v>
       </c>
       <c r="B6" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129797332</v>
+        <v>129797328</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -800,17 +800,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743452</v>
+        <v>743294</v>
       </c>
       <c r="R3" t="n">
-        <v>7092954</v>
+        <v>7092958</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129797328</v>
+        <v>129797332</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,16 +896,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -897,33 +913,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743294</v>
+        <v>743452</v>
       </c>
       <c r="R4" t="n">
-        <v>7092958</v>
+        <v>7092954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
         <v>129797334</v>
       </c>
       <c r="B6" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129797332</v>
+        <v>129797328</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -800,17 +800,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743452</v>
+        <v>743294</v>
       </c>
       <c r="R3" t="n">
-        <v>7092954</v>
+        <v>7092958</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129797328</v>
+        <v>129797332</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,16 +896,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -897,33 +913,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743294</v>
+        <v>743452</v>
       </c>
       <c r="R4" t="n">
-        <v>7092958</v>
+        <v>7092954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129797330</v>
       </c>
       <c r="B2" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129797328</v>
+        <v>129797332</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -800,33 +800,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743294</v>
+        <v>743452</v>
       </c>
       <c r="R3" t="n">
-        <v>7092958</v>
+        <v>7092954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129797332</v>
+        <v>129797328</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -913,17 +897,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743452</v>
+        <v>743294</v>
       </c>
       <c r="R4" t="n">
-        <v>7092954</v>
+        <v>7092958</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
         <v>129797335</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129797334</v>
       </c>
       <c r="B6" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>129797331</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129797332</v>
+        <v>129797328</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -800,17 +800,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743452</v>
+        <v>743294</v>
       </c>
       <c r="R3" t="n">
-        <v>7092954</v>
+        <v>7092958</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129797328</v>
+        <v>129797332</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,16 +896,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -897,33 +913,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743294</v>
+        <v>743452</v>
       </c>
       <c r="R4" t="n">
-        <v>7092958</v>
+        <v>7092954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129797330</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129797328</v>
+        <v>129797332</v>
       </c>
       <c r="B3" t="n">
         <v>57737</v>
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -800,33 +800,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743294</v>
+        <v>743452</v>
       </c>
       <c r="R3" t="n">
-        <v>7092958</v>
+        <v>7092954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129797332</v>
+        <v>129797328</v>
       </c>
       <c r="B4" t="n">
-        <v>57734</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -913,17 +897,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743452</v>
+        <v>743294</v>
       </c>
       <c r="R4" t="n">
-        <v>7092954</v>
+        <v>7092958</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
         <v>129797335</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129797334</v>
       </c>
       <c r="B6" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>129797331</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>129797334</v>
       </c>
       <c r="B6" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>129797334</v>
       </c>
       <c r="B6" t="n">
-        <v>91904</v>
+        <v>91921</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>129797334</v>
       </c>
       <c r="B6" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>130191660</v>
       </c>
       <c r="B9" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>130191653</v>
       </c>
       <c r="B12" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>130191673</v>
       </c>
       <c r="B13" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>130191663</v>
       </c>
       <c r="B15" t="n">
-        <v>98748</v>
+        <v>98750</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -1289,7 +1289,7 @@
         <v>130191672</v>
       </c>
       <c r="B8" t="n">
-        <v>43995</v>
+        <v>44080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130191660</v>
+        <v>130191676</v>
       </c>
       <c r="B9" t="n">
-        <v>91641</v>
+        <v>44080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>101735</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743590</v>
+        <v>743575</v>
       </c>
       <c r="R9" t="n">
-        <v>7092922</v>
+        <v>7093060</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1510,32 +1510,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130191676</v>
+        <v>130191660</v>
       </c>
       <c r="B10" t="n">
-        <v>43995</v>
+        <v>91728</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101735</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743575</v>
+        <v>743590</v>
       </c>
       <c r="R10" t="n">
-        <v>7093060</v>
+        <v>7092922</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1625,7 +1625,7 @@
         <v>130191669</v>
       </c>
       <c r="B11" t="n">
-        <v>43995</v>
+        <v>44080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>130191653</v>
       </c>
       <c r="B12" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>130191673</v>
       </c>
       <c r="B13" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>130191675</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>130191663</v>
       </c>
       <c r="B15" t="n">
-        <v>98750</v>
+        <v>98837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -1734,7 +1734,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130191653</v>
+        <v>130191673</v>
       </c>
       <c r="B12" t="n">
         <v>91692</v>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>743443</v>
+        <v>743567</v>
       </c>
       <c r="R12" t="n">
-        <v>7092908</v>
+        <v>7093054</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130191673</v>
+        <v>130191653</v>
       </c>
       <c r="B13" t="n">
         <v>91692</v>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>743567</v>
+        <v>743443</v>
       </c>
       <c r="R13" t="n">
-        <v>7093054</v>
+        <v>7092908</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -1398,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130191676</v>
+        <v>130191660</v>
       </c>
       <c r="B9" t="n">
-        <v>44080</v>
+        <v>91728</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101735</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743575</v>
+        <v>743590</v>
       </c>
       <c r="R9" t="n">
-        <v>7093060</v>
+        <v>7092922</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1510,32 +1510,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130191660</v>
+        <v>130191676</v>
       </c>
       <c r="B10" t="n">
-        <v>91728</v>
+        <v>44080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>101735</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743590</v>
+        <v>743575</v>
       </c>
       <c r="R10" t="n">
-        <v>7092922</v>
+        <v>7093060</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1734,7 +1734,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130191673</v>
+        <v>130191653</v>
       </c>
       <c r="B12" t="n">
         <v>91692</v>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>743567</v>
+        <v>743443</v>
       </c>
       <c r="R12" t="n">
-        <v>7093054</v>
+        <v>7092908</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130191653</v>
+        <v>130191673</v>
       </c>
       <c r="B13" t="n">
         <v>91692</v>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>743443</v>
+        <v>743567</v>
       </c>
       <c r="R13" t="n">
-        <v>7092908</v>
+        <v>7093054</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -1513,7 +1513,7 @@
         <v>130191660</v>
       </c>
       <c r="B10" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>130191653</v>
       </c>
       <c r="B12" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>130191673</v>
       </c>
       <c r="B13" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>130191675</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>130191663</v>
       </c>
       <c r="B15" t="n">
-        <v>98837</v>
+        <v>98840</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -1289,7 +1289,7 @@
         <v>130191672</v>
       </c>
       <c r="B8" t="n">
-        <v>44080</v>
+        <v>44106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130191676</v>
+        <v>130191660</v>
       </c>
       <c r="B9" t="n">
-        <v>44080</v>
+        <v>91757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101735</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743575</v>
+        <v>743590</v>
       </c>
       <c r="R9" t="n">
-        <v>7093060</v>
+        <v>7092922</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1510,32 +1510,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130191660</v>
+        <v>130191676</v>
       </c>
       <c r="B10" t="n">
-        <v>91731</v>
+        <v>44106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>101735</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743590</v>
+        <v>743575</v>
       </c>
       <c r="R10" t="n">
-        <v>7092922</v>
+        <v>7093060</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1625,7 +1625,7 @@
         <v>130191669</v>
       </c>
       <c r="B11" t="n">
-        <v>44080</v>
+        <v>44106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130191653</v>
+        <v>130191673</v>
       </c>
       <c r="B12" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>743443</v>
+        <v>743567</v>
       </c>
       <c r="R12" t="n">
-        <v>7092908</v>
+        <v>7093054</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1839,17 +1839,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130191673</v>
+        <v>130191653</v>
       </c>
       <c r="B13" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>743567</v>
+        <v>743443</v>
       </c>
       <c r="R13" t="n">
-        <v>7093054</v>
+        <v>7092908</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1961,7 +1961,7 @@
         <v>130191675</v>
       </c>
       <c r="B14" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>130191663</v>
       </c>
       <c r="B15" t="n">
-        <v>98840</v>
+        <v>98866</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -1401,7 +1401,7 @@
         <v>130191660</v>
       </c>
       <c r="B9" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130191673</v>
+        <v>130191653</v>
       </c>
       <c r="B12" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>743567</v>
+        <v>743443</v>
       </c>
       <c r="R12" t="n">
-        <v>7093054</v>
+        <v>7092908</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1839,17 +1839,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130191653</v>
+        <v>130191673</v>
       </c>
       <c r="B13" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>743443</v>
+        <v>743567</v>
       </c>
       <c r="R13" t="n">
-        <v>7092908</v>
+        <v>7093054</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2073,7 +2073,7 @@
         <v>130191663</v>
       </c>
       <c r="B15" t="n">
-        <v>98866</v>
+        <v>98867</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -1401,7 +1401,7 @@
         <v>130191660</v>
       </c>
       <c r="B9" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>130191653</v>
       </c>
       <c r="B12" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>130191673</v>
       </c>
       <c r="B13" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>130191663</v>
       </c>
       <c r="B15" t="n">
-        <v>98867</v>
+        <v>98868</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -1289,7 +1289,7 @@
         <v>130191672</v>
       </c>
       <c r="B8" t="n">
-        <v>44106</v>
+        <v>44108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>130191660</v>
       </c>
       <c r="B9" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>130191676</v>
       </c>
       <c r="B10" t="n">
-        <v>44106</v>
+        <v>44108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>130191669</v>
       </c>
       <c r="B11" t="n">
-        <v>44106</v>
+        <v>44108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>130191653</v>
       </c>
       <c r="B12" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>130191673</v>
       </c>
       <c r="B13" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>130191675</v>
       </c>
       <c r="B14" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>130191663</v>
       </c>
       <c r="B15" t="n">
-        <v>98868</v>
+        <v>98870</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -1734,7 +1734,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130191653</v>
+        <v>130191673</v>
       </c>
       <c r="B12" t="n">
         <v>91725</v>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>743443</v>
+        <v>743567</v>
       </c>
       <c r="R12" t="n">
-        <v>7092908</v>
+        <v>7093054</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130191673</v>
+        <v>130191653</v>
       </c>
       <c r="B13" t="n">
         <v>91725</v>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>743567</v>
+        <v>743443</v>
       </c>
       <c r="R13" t="n">
-        <v>7093054</v>
+        <v>7092908</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2073,7 +2073,7 @@
         <v>130191663</v>
       </c>
       <c r="B15" t="n">
-        <v>98870</v>
+        <v>98874</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129797330</v>
+        <v>129797334</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743926</v>
+        <v>743551</v>
       </c>
       <c r="R2" t="n">
-        <v>7093082</v>
+        <v>7093080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129797332</v>
+        <v>130191660</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Halvfaritberget, Vb</t>
+          <t>Umeå-Örnsköldsvik, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743452</v>
+        <v>743590</v>
       </c>
       <c r="R3" t="n">
-        <v>7092954</v>
+        <v>7092922</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,73 +872,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129797328</v>
+        <v>130191653</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Halvfaritberget, Vb</t>
+          <t>Umeå-Örnsköldsvik, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743294</v>
+        <v>743443</v>
       </c>
       <c r="R4" t="n">
-        <v>7092958</v>
+        <v>7092908</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,12 +949,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,65 +984,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129797335</v>
+        <v>130191673</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Halvfaritberget, Vb</t>
+          <t>Umeå-Örnsköldsvik, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743855</v>
+        <v>743567</v>
       </c>
       <c r="R5" t="n">
-        <v>7092956</v>
+        <v>7093054</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,17 +1061,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>NVI (C250260) Calluna AB</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1080,57 +1096,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129797334</v>
+        <v>130191675</v>
       </c>
       <c r="B6" t="n">
-        <v>91939</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Halvfaritberget, Vb</t>
+          <t>Umeå-Örnsköldsvik, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>743551</v>
+        <v>743567</v>
       </c>
       <c r="R6" t="n">
-        <v>7093080</v>
+        <v>7093056</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,12 +1173,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,26 +1208,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129797331</v>
+        <v>129797330</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1224,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>743453</v>
+        <v>743926</v>
       </c>
       <c r="R7" t="n">
-        <v>7092998</v>
+        <v>7093082</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130191672</v>
+        <v>129797331</v>
       </c>
       <c r="B8" t="n">
-        <v>44108</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,34 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101735</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Umeå-Örnsköldsvik, Vb</t>
+          <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>743554</v>
+        <v>743453</v>
       </c>
       <c r="R8" t="n">
-        <v>7093045</v>
+        <v>7092998</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1351,27 +1382,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>NVI (C250260) Calluna AB</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,57 +1402,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130191660</v>
+        <v>129797332</v>
       </c>
       <c r="B9" t="n">
-        <v>91761</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Umeå-Örnsköldsvik, Vb</t>
+          <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743590</v>
+        <v>743452</v>
       </c>
       <c r="R9" t="n">
-        <v>7092922</v>
+        <v>7092954</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,27 +1479,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>NVI (C250260) Calluna AB</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,22 +1499,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130191676</v>
+        <v>129797333</v>
       </c>
       <c r="B10" t="n">
-        <v>44108</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,34 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101735</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Umeå-Örnsköldsvik, Vb</t>
+          <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743575</v>
+        <v>743219</v>
       </c>
       <c r="R10" t="n">
-        <v>7093060</v>
+        <v>7092841</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,27 +1576,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>NVI (C250260) Calluna AB</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,57 +1596,73 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130191669</v>
+        <v>129797328</v>
       </c>
       <c r="B11" t="n">
-        <v>44108</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Umeå-Örnsköldsvik, Vb</t>
+          <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>743533</v>
+        <v>743294</v>
       </c>
       <c r="R11" t="n">
-        <v>7092980</v>
+        <v>7092958</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,27 +1689,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>NVI (C250260) Calluna AB</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,57 +1709,65 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130191673</v>
+        <v>129797335</v>
       </c>
       <c r="B12" t="n">
-        <v>91725</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Umeå-Örnsköldsvik, Vb</t>
+          <t>Halvfaritberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>743567</v>
+        <v>743855</v>
       </c>
       <c r="R12" t="n">
-        <v>7093054</v>
+        <v>7092956</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,27 +1794,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>NVI (C250260) Calluna AB</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1834,22 +1819,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130191653</v>
+        <v>130191669</v>
       </c>
       <c r="B13" t="n">
-        <v>91725</v>
+        <v>44177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,21 +1842,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>101735</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>743443</v>
+        <v>743533</v>
       </c>
       <c r="R13" t="n">
-        <v>7092908</v>
+        <v>7092980</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,7 +1901,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1926,7 +1911,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1951,39 +1936,39 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130191675</v>
+        <v>130191672</v>
       </c>
       <c r="B14" t="n">
-        <v>79211</v>
+        <v>44177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1993,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>743567</v>
+        <v>743554</v>
       </c>
       <c r="R14" t="n">
-        <v>7093056</v>
+        <v>7093045</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,7 +2013,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2038,7 +2023,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2070,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130191663</v>
+        <v>130191676</v>
       </c>
       <c r="B15" t="n">
-        <v>98874</v>
+        <v>44177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,21 +2066,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>101735</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2105,10 +2090,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>743574</v>
+        <v>743575</v>
       </c>
       <c r="R15" t="n">
-        <v>7092954</v>
+        <v>7093060</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2140,7 +2125,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2150,7 +2135,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2179,6 +2164,215 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129797337</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Halvfaritberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>744042</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7092976</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130191663</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Umeå-Örnsköldsvik, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>743574</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7092954</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50033-2025 artfynd.xlsx
+++ b/artfynd/A 50033-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797334</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191660</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191653</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191673</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191675</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797330</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797331</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797332</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797333</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1718,6 +1768,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797328</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1828,6 +1883,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797335</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1940,6 +2000,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191669</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2052,6 +2117,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191672</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2164,6 +2234,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191676</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2261,6 +2336,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797337</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2373,8 +2453,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191663</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>